--- a/chapters/collection/admin_secondary.xlsx
+++ b/chapters/collection/admin_secondary.xlsx
@@ -1684,7 +1684,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notes for the analyst</t>
+          <t>Notes for the analyst (a realistic teaching dataset written for the book)</t>
         </is>
       </c>
     </row>
